--- a/clinical_tables/clinical_DENV.xlsx
+++ b/clinical_tables/clinical_DENV.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="79">
   <si>
     <t>Category</t>
   </si>
@@ -71,22 +71,19 @@
     <t>15-19</t>
   </si>
   <si>
-    <t>20-29</t>
-  </si>
-  <si>
-    <t>30-39</t>
-  </si>
-  <si>
-    <t>40-49</t>
+    <t>20-39</t>
+  </si>
+  <si>
+    <t>40-59</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>50-59</t>
-  </si>
-  <si>
-    <t>60-69</t>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
   </si>
   <si>
     <t>70-79</t>
@@ -606,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1">
@@ -652,16 +649,16 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>37937</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>8056</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9264</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>42031</v>
       </c>
       <c r="F2">
         <v>25093</v>
@@ -682,7 +679,7 @@
         <v>43353</v>
       </c>
       <c r="L2">
-        <v>17983</v>
+        <v>18197</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -690,16 +687,16 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>102922</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>17773</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19622</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>116625</v>
       </c>
       <c r="F3">
         <v>61865</v>
@@ -720,7 +717,7 @@
         <v>100855</v>
       </c>
       <c r="L3">
-        <v>35461</v>
+        <v>35639</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -728,16 +725,16 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>148449</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>26895</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>26134</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>144775</v>
       </c>
       <c r="F4">
         <v>77180</v>
@@ -758,7 +755,7 @@
         <v>134790</v>
       </c>
       <c r="L4">
-        <v>47968</v>
+        <v>48298</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -766,37 +763,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>575102</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>96936</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>102888</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>582346</v>
       </c>
       <c r="F5">
-        <v>186551</v>
+        <v>361701</v>
       </c>
       <c r="G5">
-        <v>104009</v>
+        <v>201688</v>
       </c>
       <c r="H5">
-        <v>261326</v>
+        <v>498773</v>
       </c>
       <c r="I5">
-        <v>318570</v>
+        <v>596148</v>
       </c>
       <c r="J5">
-        <v>1204789</v>
+        <v>2266673</v>
       </c>
       <c r="K5">
-        <v>304651</v>
+        <v>581717</v>
       </c>
       <c r="L5">
-        <v>100941</v>
+        <v>177963</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -804,37 +801,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>382253</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>54431</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>63144</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>399945</v>
       </c>
       <c r="F6">
-        <v>175150</v>
+        <v>263086</v>
       </c>
       <c r="G6">
-        <v>97679</v>
+        <v>143083</v>
       </c>
       <c r="H6">
-        <v>237447</v>
+        <v>368661</v>
       </c>
       <c r="I6">
-        <v>277578</v>
+        <v>426092</v>
       </c>
       <c r="J6">
-        <v>1061884</v>
+        <v>1783483</v>
       </c>
       <c r="K6">
-        <v>277066</v>
+        <v>446491</v>
       </c>
       <c r="L6">
-        <v>75701</v>
+        <v>105048</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -842,37 +839,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>65623</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>12592</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>15171</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>81843</v>
       </c>
       <c r="F7">
-        <v>147646</v>
+        <v>45855</v>
       </c>
       <c r="G7">
-        <v>82086</v>
+        <v>32406</v>
       </c>
       <c r="H7">
-        <v>206084</v>
+        <v>79507</v>
       </c>
       <c r="I7">
-        <v>242915</v>
+        <v>94707</v>
       </c>
       <c r="J7">
-        <v>998333</v>
+        <v>346851</v>
       </c>
       <c r="K7">
-        <v>254715</v>
+        <v>86538</v>
       </c>
       <c r="L7">
-        <v>62286</v>
+        <v>31601</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -880,37 +877,37 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>57572</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>7578</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>8967</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>62232</v>
       </c>
       <c r="F8">
-        <v>45855</v>
+        <v>39035</v>
       </c>
       <c r="G8">
-        <v>32406</v>
+        <v>20704</v>
       </c>
       <c r="H8">
-        <v>79507</v>
+        <v>60049</v>
       </c>
       <c r="I8">
-        <v>94707</v>
+        <v>69597</v>
       </c>
       <c r="J8">
-        <v>346851</v>
+        <v>312687</v>
       </c>
       <c r="K8">
-        <v>86538</v>
+        <v>76326</v>
       </c>
       <c r="L8">
-        <v>31348</v>
+        <v>15421</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -918,37 +915,37 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>41590</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>5602</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>6253</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>43554</v>
       </c>
       <c r="F9">
-        <v>115440</v>
+        <v>28364</v>
       </c>
       <c r="G9">
-        <v>60997</v>
+        <v>14844</v>
       </c>
       <c r="H9">
-        <v>162577</v>
+        <v>45247</v>
       </c>
       <c r="I9">
-        <v>183177</v>
+        <v>52949</v>
       </c>
       <c r="J9">
-        <v>785150</v>
+        <v>245157</v>
       </c>
       <c r="K9">
-        <v>191776</v>
+        <v>59855</v>
       </c>
       <c r="L9">
-        <v>42155</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -956,37 +953,37 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>46946</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>6097</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>6555</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>44215</v>
       </c>
       <c r="F10">
-        <v>67399</v>
+        <v>30103</v>
       </c>
       <c r="G10">
-        <v>35548</v>
+        <v>15660</v>
       </c>
       <c r="H10">
-        <v>105296</v>
+        <v>52650</v>
       </c>
       <c r="I10">
-        <v>122546</v>
+        <v>60004</v>
       </c>
       <c r="J10">
-        <v>557844</v>
+        <v>292661</v>
       </c>
       <c r="K10">
-        <v>136181</v>
+        <v>70734</v>
       </c>
       <c r="L10">
-        <v>26623</v>
+        <v>13110</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -994,37 +991,37 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>18754</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2585</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2452</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>15704</v>
       </c>
       <c r="F11">
-        <v>30103</v>
+        <v>10974</v>
       </c>
       <c r="G11">
-        <v>15660</v>
+        <v>5633</v>
       </c>
       <c r="H11">
-        <v>52650</v>
+        <v>20022</v>
       </c>
       <c r="I11">
-        <v>60004</v>
+        <v>23649</v>
       </c>
       <c r="J11">
-        <v>292661</v>
+        <v>116966</v>
       </c>
       <c r="K11">
-        <v>70734</v>
+        <v>28646</v>
       </c>
       <c r="L11">
-        <v>13022</v>
+        <v>5354</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1032,37 +1029,37 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>21735</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>4684</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>4987</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>20603</v>
       </c>
       <c r="F12">
-        <v>10974</v>
+        <v>13090</v>
       </c>
       <c r="G12">
-        <v>5633</v>
+        <v>7562</v>
       </c>
       <c r="H12">
-        <v>20022</v>
+        <v>13899</v>
       </c>
       <c r="I12">
-        <v>23649</v>
+        <v>14609</v>
       </c>
       <c r="J12">
-        <v>116966</v>
+        <v>51593</v>
       </c>
       <c r="K12">
-        <v>28646</v>
+        <v>13903</v>
       </c>
       <c r="L12">
-        <v>5322</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1070,74 +1067,36 @@
         <v>23</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>16650</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="F13">
-        <v>13090</v>
+        <v>117</v>
       </c>
       <c r="G13">
-        <v>7562</v>
+        <v>139</v>
       </c>
       <c r="H13">
-        <v>13899</v>
+        <v>11507</v>
       </c>
       <c r="I13">
-        <v>14609</v>
+        <v>55</v>
       </c>
       <c r="J13">
-        <v>51593</v>
+        <v>112</v>
       </c>
       <c r="K13">
-        <v>13903</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>6508</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14">
-        <v>1515533</v>
-      </c>
-      <c r="C14">
-        <v>243248</v>
-      </c>
-      <c r="D14">
-        <v>265460</v>
-      </c>
-      <c r="E14">
-        <v>1554126</v>
-      </c>
-      <c r="F14">
-        <v>117</v>
-      </c>
-      <c r="G14">
-        <v>139</v>
-      </c>
-      <c r="H14">
-        <v>11507</v>
-      </c>
-      <c r="I14">
-        <v>55</v>
-      </c>
-      <c r="J14">
-        <v>112</v>
-      </c>
-      <c r="K14">
-        <v>7</v>
-      </c>
-      <c r="L14">
         <v>5</v>
       </c>
     </row>
@@ -1191,7 +1150,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>3794</v>
@@ -1224,12 +1183,12 @@
         <v>5921</v>
       </c>
       <c r="L2">
-        <v>1842</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3">
         <v>133</v>
@@ -1262,12 +1221,12 @@
         <v>36162</v>
       </c>
       <c r="L3">
-        <v>21158</v>
+        <v>21465</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>42</v>
@@ -1300,12 +1259,12 @@
         <v>6857</v>
       </c>
       <c r="L4">
-        <v>9841</v>
+        <v>9977</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5">
         <v>106</v>
@@ -1338,12 +1297,12 @@
         <v>38</v>
       </c>
       <c r="L5">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>1511458</v>
@@ -1376,12 +1335,12 @@
         <v>1560744</v>
       </c>
       <c r="L6">
-        <v>414621</v>
+        <v>417418</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1414,7 +1373,7 @@
         <v>33493</v>
       </c>
       <c r="L7">
-        <v>17748</v>
+        <v>17700</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +1426,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>856174</v>
@@ -1500,12 +1459,12 @@
         <v>892251</v>
       </c>
       <c r="L2">
-        <v>251047</v>
+        <v>252816</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>2712</v>
@@ -1538,12 +1497,12 @@
         <v>1205</v>
       </c>
       <c r="L3">
-        <v>307</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>185</v>
@@ -1581,7 +1540,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>656462</v>
@@ -1614,7 +1573,7 @@
         <v>749757</v>
       </c>
       <c r="L5">
-        <v>213969</v>
+        <v>215456</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +1626,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1054457</v>
@@ -1700,12 +1659,12 @@
         <v>1444481</v>
       </c>
       <c r="L2">
-        <v>349185</v>
+        <v>352455</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>54</v>
@@ -1743,7 +1702,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>9674</v>
@@ -1776,12 +1735,12 @@
         <v>35105</v>
       </c>
       <c r="L4">
-        <v>11892</v>
+        <v>12060</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>36368</v>
@@ -1819,7 +1778,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>1034</v>
@@ -1852,12 +1811,12 @@
         <v>2687</v>
       </c>
       <c r="L6">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -1895,7 +1854,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>1339</v>
@@ -1928,12 +1887,12 @@
         <v>1181</v>
       </c>
       <c r="L8">
-        <v>30185</v>
+        <v>29320</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>412591</v>
@@ -1966,12 +1925,12 @@
         <v>158115</v>
       </c>
       <c r="L9">
-        <v>69202</v>
+        <v>69918</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -2009,7 +1968,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2042,7 +2001,7 @@
         <v>1646</v>
       </c>
       <c r="L11">
-        <v>4091</v>
+        <v>4021</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2054,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>771014</v>
@@ -2128,12 +2087,12 @@
         <v>963025</v>
       </c>
       <c r="L2">
-        <v>220414</v>
+        <v>222718</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>18895</v>
@@ -2166,12 +2125,12 @@
         <v>22480</v>
       </c>
       <c r="L3">
-        <v>18328</v>
+        <v>17929</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>398656</v>
@@ -2204,12 +2163,12 @@
         <v>143944</v>
       </c>
       <c r="L4">
-        <v>88651</v>
+        <v>88571</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>326968</v>
@@ -2242,12 +2201,12 @@
         <v>512128</v>
       </c>
       <c r="L5">
-        <v>133807</v>
+        <v>135280</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2280,7 +2239,7 @@
         <v>1638</v>
       </c>
       <c r="L6">
-        <v>4123</v>
+        <v>4052</v>
       </c>
     </row>
   </sheetData>
@@ -2333,7 +2292,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>1007100</v>
@@ -2366,12 +2325,12 @@
         <v>1391658</v>
       </c>
       <c r="L2">
-        <v>331082</v>
+        <v>335084</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>20895</v>
@@ -2404,12 +2363,12 @@
         <v>39298</v>
       </c>
       <c r="L3">
-        <v>14310</v>
+        <v>14361</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>486230</v>
@@ -2442,12 +2401,12 @@
         <v>207772</v>
       </c>
       <c r="L4">
-        <v>114024</v>
+        <v>113301</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>385</v>
@@ -2485,7 +2444,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>728</v>
@@ -2518,12 +2477,12 @@
         <v>1856</v>
       </c>
       <c r="L6">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>195</v>
@@ -2556,12 +2515,12 @@
         <v>495</v>
       </c>
       <c r="L7">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2594,7 +2553,7 @@
         <v>2091</v>
       </c>
       <c r="L8">
-        <v>5320</v>
+        <v>5214</v>
       </c>
     </row>
   </sheetData>
@@ -2647,7 +2606,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>2260</v>
@@ -2680,12 +2639,12 @@
         <v>8659</v>
       </c>
       <c r="L2">
-        <v>1896</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>19340</v>
@@ -2718,12 +2677,12 @@
         <v>8182</v>
       </c>
       <c r="L3">
-        <v>6895</v>
+        <v>7141</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>1832</v>
@@ -2756,12 +2715,12 @@
         <v>2424</v>
       </c>
       <c r="L4">
-        <v>560</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>7510</v>
@@ -2794,12 +2753,12 @@
         <v>4911</v>
       </c>
       <c r="L5">
-        <v>1483</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>67800</v>
@@ -2832,12 +2791,12 @@
         <v>32451</v>
       </c>
       <c r="L6">
-        <v>24234</v>
+        <v>24661</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>49767</v>
@@ -2870,12 +2829,12 @@
         <v>5492</v>
       </c>
       <c r="L7">
-        <v>18286</v>
+        <v>18329</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8">
         <v>19595</v>
@@ -2908,12 +2867,12 @@
         <v>10934</v>
       </c>
       <c r="L8">
-        <v>4082</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>43108</v>
@@ -2946,12 +2905,12 @@
         <v>34326</v>
       </c>
       <c r="L9">
-        <v>20050</v>
+        <v>20013</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>129466</v>
@@ -2984,12 +2943,12 @@
         <v>105827</v>
       </c>
       <c r="L10">
-        <v>114173</v>
+        <v>114982</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>23866</v>
@@ -3022,12 +2981,12 @@
         <v>5489</v>
       </c>
       <c r="L11">
-        <v>13413</v>
+        <v>13586</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <v>21287</v>
@@ -3060,12 +3019,12 @@
         <v>35326</v>
       </c>
       <c r="L12">
-        <v>12411</v>
+        <v>12423</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>46869</v>
@@ -3098,12 +3057,12 @@
         <v>13001</v>
       </c>
       <c r="L13">
-        <v>3805</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>529017</v>
@@ -3136,12 +3095,12 @@
         <v>161667</v>
       </c>
       <c r="L14">
-        <v>62305</v>
+        <v>62859</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15">
         <v>10871</v>
@@ -3174,12 +3133,12 @@
         <v>16874</v>
       </c>
       <c r="L15">
-        <v>10156</v>
+        <v>10312</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>35770</v>
@@ -3212,12 +3171,12 @@
         <v>7821</v>
       </c>
       <c r="L16">
-        <v>7287</v>
+        <v>7390</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>63175</v>
@@ -3250,12 +3209,12 @@
         <v>107485</v>
       </c>
       <c r="L17">
-        <v>11213</v>
+        <v>11447</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>62627</v>
@@ -3288,12 +3247,12 @@
         <v>21378</v>
       </c>
       <c r="L18">
-        <v>23019</v>
+        <v>23244</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19">
         <v>5297</v>
@@ -3326,12 +3285,12 @@
         <v>9341</v>
       </c>
       <c r="L19">
-        <v>18970</v>
+        <v>19134</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20">
         <v>57056</v>
@@ -3364,12 +3323,12 @@
         <v>9452</v>
       </c>
       <c r="L20">
-        <v>7781</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21">
         <v>3199</v>
@@ -3402,12 +3361,12 @@
         <v>85636</v>
       </c>
       <c r="L21">
-        <v>6706</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22">
         <v>88142</v>
@@ -3440,12 +3399,12 @@
         <v>29441</v>
       </c>
       <c r="L22">
-        <v>7186</v>
+        <v>7187</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23">
         <v>7908</v>
@@ -3478,12 +3437,12 @@
         <v>2552</v>
       </c>
       <c r="L23">
-        <v>1542</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24">
         <v>217</v>
@@ -3516,12 +3475,12 @@
         <v>439</v>
       </c>
       <c r="L24">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>5171</v>
@@ -3554,12 +3513,12 @@
         <v>25558</v>
       </c>
       <c r="L25">
-        <v>3173</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26">
         <v>202804</v>
@@ -3592,12 +3551,12 @@
         <v>894683</v>
       </c>
       <c r="L26">
-        <v>67538</v>
+        <v>68145</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27">
         <v>3609</v>
@@ -3630,12 +3589,12 @@
         <v>792</v>
       </c>
       <c r="L27">
-        <v>1128</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28">
         <v>7970</v>
@@ -3668,7 +3627,7 @@
         <v>3074</v>
       </c>
       <c r="L28">
-        <v>15343</v>
+        <v>14998</v>
       </c>
     </row>
   </sheetData>
@@ -3721,7 +3680,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>48972</v>
@@ -3754,12 +3713,12 @@
         <v>28890</v>
       </c>
       <c r="L2">
-        <v>9907</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>783527</v>
@@ -3792,12 +3751,12 @@
         <v>362266</v>
       </c>
       <c r="L3">
-        <v>112644</v>
+        <v>112955</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>650813</v>
@@ -3830,12 +3789,12 @@
         <v>1179744</v>
       </c>
       <c r="L4">
-        <v>313466</v>
+        <v>315975</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>32221</v>
@@ -3868,12 +3827,12 @@
         <v>72313</v>
       </c>
       <c r="L5">
-        <v>29305</v>
+        <v>29595</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3959,7 +3918,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>760276</v>
@@ -3992,12 +3951,12 @@
         <v>1608963</v>
       </c>
       <c r="L2">
-        <v>182851</v>
+        <v>183454</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>360</v>
@@ -4030,12 +3989,12 @@
         <v>23</v>
       </c>
       <c r="L3">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>11068</v>
@@ -4068,12 +4027,12 @@
         <v>2867</v>
       </c>
       <c r="L4">
-        <v>49005</v>
+        <v>49578</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>646301</v>
@@ -4106,12 +4065,12 @@
         <v>30074</v>
       </c>
       <c r="L5">
-        <v>163671</v>
+        <v>165200</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6">
         <v>97528</v>
@@ -4144,12 +4103,12 @@
         <v>928</v>
       </c>
       <c r="L6">
-        <v>68859</v>
+        <v>69380</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4182,7 +4141,7 @@
         <v>360</v>
       </c>
       <c r="L7">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -4235,7 +4194,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>809162</v>
@@ -4268,12 +4227,12 @@
         <v>804403</v>
       </c>
       <c r="L2">
-        <v>227488</v>
+        <v>228194</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>314</v>
@@ -4306,12 +4265,12 @@
         <v>1398</v>
       </c>
       <c r="L3">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>1283</v>
@@ -4344,12 +4303,12 @@
         <v>10476</v>
       </c>
       <c r="L4">
-        <v>5060</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>701234</v>
@@ -4382,12 +4341,12 @@
         <v>777973</v>
       </c>
       <c r="L5">
-        <v>198917</v>
+        <v>200866</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6">
         <v>3540</v>
@@ -4420,12 +4379,12 @@
         <v>48816</v>
       </c>
       <c r="L6">
-        <v>32972</v>
+        <v>33448</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4458,7 +4417,7 @@
         <v>149</v>
       </c>
       <c r="L7">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4511,7 +4470,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>684056</v>
@@ -4544,12 +4503,12 @@
         <v>1608963</v>
       </c>
       <c r="L2">
-        <v>202915</v>
+        <v>203373</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>2773</v>
@@ -4582,12 +4541,12 @@
         <v>330</v>
       </c>
       <c r="L3">
-        <v>1539</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>16292</v>
@@ -4620,12 +4579,12 @@
         <v>1577</v>
       </c>
       <c r="L4">
-        <v>14972</v>
+        <v>15137</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>592689</v>
@@ -4658,12 +4617,12 @@
         <v>30432</v>
       </c>
       <c r="L5">
-        <v>191260</v>
+        <v>193100</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6">
         <v>219723</v>
@@ -4696,12 +4655,12 @@
         <v>1633</v>
       </c>
       <c r="L6">
-        <v>54350</v>
+        <v>55096</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4734,7 +4693,7 @@
         <v>280</v>
       </c>
       <c r="L7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
